--- a/docs/BAO CAO TUAN - DUONG TRONG THANG - 05-10-2026.xlsx
+++ b/docs/BAO CAO TUAN - DUONG TRONG THANG - 05-10-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\13. Duong Trong Thang\Tai lieu\1. Du an chuan hoa quy trinh\VNTECH_ERP_V5_3_0_MASTER_BASELINE_R1_1_1_PROJECT_NAV_FINAL_FP_FIXED_20260908\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BCA9E7F-ED49-4E3B-958A-3627DFFA2AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D586B02F-C5B2-4AAD-BA31-E7CB44538ABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -439,7 +439,7 @@
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -518,6 +518,13 @@
       <sz val="12"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -748,14 +755,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="298">
+  <cellXfs count="296">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
@@ -1293,9 +1301,6 @@
     <xf numFmtId="1" fontId="6" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1468,12 +1473,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1584,12 +1583,16 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="9" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="5">
+  <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Normal 3" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Percent" xfId="5" builtinId="5"/>
     <cellStyle name="Percent 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -3139,65 +3142,65 @@
       </c>
     </row>
     <row r="6" spans="1:16" ht="18" customHeight="1">
-      <c r="A6" s="288" t="s">
+      <c r="A6" s="285" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="289"/>
-      <c r="C6" s="289"/>
-      <c r="D6" s="289"/>
-      <c r="E6" s="289"/>
-      <c r="F6" s="289"/>
-      <c r="G6" s="289"/>
-      <c r="H6" s="290"/>
-      <c r="I6" s="291" t="s">
+      <c r="B6" s="286"/>
+      <c r="C6" s="286"/>
+      <c r="D6" s="286"/>
+      <c r="E6" s="286"/>
+      <c r="F6" s="286"/>
+      <c r="G6" s="286"/>
+      <c r="H6" s="287"/>
+      <c r="I6" s="288" t="s">
         <v>60</v>
       </c>
-      <c r="J6" s="292"/>
-      <c r="K6" s="292"/>
-      <c r="L6" s="292"/>
-      <c r="M6" s="292"/>
-      <c r="N6" s="292"/>
-      <c r="O6" s="293"/>
+      <c r="J6" s="289"/>
+      <c r="K6" s="289"/>
+      <c r="L6" s="289"/>
+      <c r="M6" s="289"/>
+      <c r="N6" s="289"/>
+      <c r="O6" s="290"/>
       <c r="P6" s="14"/>
     </row>
     <row r="7" spans="1:16" ht="15" customHeight="1">
-      <c r="A7" s="294" t="s">
+      <c r="A7" s="291" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="294" t="s">
+      <c r="B7" s="291" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="283" t="s">
+      <c r="C7" s="280" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="283"/>
-      <c r="E7" s="283"/>
-      <c r="F7" s="283"/>
-      <c r="G7" s="286" t="s">
+      <c r="D7" s="280"/>
+      <c r="E7" s="280"/>
+      <c r="F7" s="280"/>
+      <c r="G7" s="283" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="286" t="s">
+      <c r="H7" s="283" t="s">
         <v>6</v>
       </c>
-      <c r="I7" s="294" t="s">
+      <c r="I7" s="291" t="s">
         <v>2</v>
       </c>
-      <c r="J7" s="294" t="s">
+      <c r="J7" s="291" t="s">
         <v>3</v>
       </c>
-      <c r="K7" s="296" t="s">
+      <c r="K7" s="293" t="s">
         <v>4</v>
       </c>
-      <c r="L7" s="297"/>
-      <c r="M7" s="297"/>
-      <c r="N7" s="297"/>
-      <c r="O7" s="286" t="s">
+      <c r="L7" s="294"/>
+      <c r="M7" s="294"/>
+      <c r="N7" s="294"/>
+      <c r="O7" s="283" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="59.25" customHeight="1">
-      <c r="A8" s="295"/>
-      <c r="B8" s="295"/>
+      <c r="A8" s="292"/>
+      <c r="B8" s="292"/>
       <c r="C8" s="15" t="s">
         <v>7</v>
       </c>
@@ -3210,10 +3213,10 @@
       <c r="F8" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="G8" s="287"/>
-      <c r="H8" s="287"/>
-      <c r="I8" s="295"/>
-      <c r="J8" s="295"/>
+      <c r="G8" s="284"/>
+      <c r="H8" s="284"/>
+      <c r="I8" s="292"/>
+      <c r="J8" s="292"/>
       <c r="K8" s="82" t="s">
         <v>7</v>
       </c>
@@ -3226,7 +3229,7 @@
       <c r="N8" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="O8" s="287"/>
+      <c r="O8" s="284"/>
       <c r="P8" s="17"/>
     </row>
     <row r="9" spans="1:16">
@@ -4237,57 +4240,57 @@
       <c r="O55" s="57"/>
     </row>
     <row r="56" spans="2:15">
-      <c r="B56" s="284" t="s">
+      <c r="B56" s="281" t="s">
         <v>40</v>
       </c>
-      <c r="C56" s="284"/>
-      <c r="D56" s="284"/>
-      <c r="E56" s="284"/>
-      <c r="F56" s="284"/>
-      <c r="G56" s="284"/>
-      <c r="H56" s="284"/>
-      <c r="I56" s="284"/>
-      <c r="J56" s="284"/>
-      <c r="K56" s="284"/>
-      <c r="L56" s="284"/>
-      <c r="M56" s="284"/>
-      <c r="N56" s="284"/>
+      <c r="C56" s="281"/>
+      <c r="D56" s="281"/>
+      <c r="E56" s="281"/>
+      <c r="F56" s="281"/>
+      <c r="G56" s="281"/>
+      <c r="H56" s="281"/>
+      <c r="I56" s="281"/>
+      <c r="J56" s="281"/>
+      <c r="K56" s="281"/>
+      <c r="L56" s="281"/>
+      <c r="M56" s="281"/>
+      <c r="N56" s="281"/>
       <c r="O56" s="57"/>
     </row>
     <row r="57" spans="2:15" hidden="1">
-      <c r="B57" s="284" t="s">
+      <c r="B57" s="281" t="s">
         <v>41</v>
       </c>
-      <c r="C57" s="284"/>
-      <c r="D57" s="284"/>
-      <c r="E57" s="284"/>
-      <c r="F57" s="284"/>
-      <c r="G57" s="284"/>
-      <c r="H57" s="284"/>
-      <c r="I57" s="284"/>
-      <c r="J57" s="284"/>
-      <c r="K57" s="284"/>
-      <c r="L57" s="284"/>
-      <c r="M57" s="284"/>
-      <c r="N57" s="284"/>
+      <c r="C57" s="281"/>
+      <c r="D57" s="281"/>
+      <c r="E57" s="281"/>
+      <c r="F57" s="281"/>
+      <c r="G57" s="281"/>
+      <c r="H57" s="281"/>
+      <c r="I57" s="281"/>
+      <c r="J57" s="281"/>
+      <c r="K57" s="281"/>
+      <c r="L57" s="281"/>
+      <c r="M57" s="281"/>
+      <c r="N57" s="281"/>
       <c r="O57" s="57"/>
     </row>
     <row r="58" spans="2:15" hidden="1">
-      <c r="B58" s="284" t="s">
+      <c r="B58" s="281" t="s">
         <v>42</v>
       </c>
-      <c r="C58" s="284"/>
-      <c r="D58" s="284"/>
-      <c r="E58" s="284"/>
-      <c r="F58" s="284"/>
-      <c r="G58" s="284"/>
-      <c r="H58" s="284"/>
-      <c r="I58" s="284"/>
-      <c r="J58" s="284"/>
-      <c r="K58" s="284"/>
-      <c r="L58" s="284"/>
-      <c r="M58" s="284"/>
-      <c r="N58" s="284"/>
+      <c r="C58" s="281"/>
+      <c r="D58" s="281"/>
+      <c r="E58" s="281"/>
+      <c r="F58" s="281"/>
+      <c r="G58" s="281"/>
+      <c r="H58" s="281"/>
+      <c r="I58" s="281"/>
+      <c r="J58" s="281"/>
+      <c r="K58" s="281"/>
+      <c r="L58" s="281"/>
+      <c r="M58" s="281"/>
+      <c r="N58" s="281"/>
       <c r="O58" s="57"/>
     </row>
     <row r="59" spans="2:15">
@@ -4373,19 +4376,19 @@
   <cols>
     <col min="1" max="1" width="4.7109375" style="102" customWidth="1"/>
     <col min="2" max="2" width="33.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" style="203" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" style="202" customWidth="1"/>
     <col min="4" max="4" width="9.5703125" style="102" customWidth="1"/>
-    <col min="5" max="5" width="5" style="213" customWidth="1"/>
-    <col min="6" max="6" width="6.140625" style="102" customWidth="1"/>
+    <col min="5" max="5" width="5" style="212" customWidth="1"/>
+    <col min="6" max="6" width="10" style="102" customWidth="1"/>
     <col min="7" max="7" width="11.85546875" style="109" customWidth="1"/>
     <col min="8" max="9" width="9.28515625" style="102" customWidth="1"/>
     <col min="10" max="10" width="5.7109375" style="1" customWidth="1"/>
     <col min="11" max="11" width="41.5703125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.28515625" style="236" customWidth="1"/>
+    <col min="12" max="12" width="11.28515625" style="235" customWidth="1"/>
     <col min="13" max="13" width="7.42578125" style="58" customWidth="1"/>
     <col min="14" max="14" width="6.7109375" style="58" customWidth="1"/>
     <col min="15" max="15" width="9.28515625" style="181" customWidth="1"/>
-    <col min="16" max="16" width="12.140625" style="203" customWidth="1"/>
+    <col min="16" max="16" width="12.140625" style="202" customWidth="1"/>
     <col min="17" max="17" width="7.28515625" style="1" customWidth="1"/>
     <col min="18" max="18" width="6.42578125" style="1" customWidth="1"/>
     <col min="19" max="256" width="9.140625" style="1"/>
@@ -5536,7 +5539,7 @@
       </c>
       <c r="C2" s="104"/>
       <c r="D2" s="106"/>
-      <c r="E2" s="214"/>
+      <c r="E2" s="213"/>
       <c r="F2" s="106"/>
       <c r="G2" s="111"/>
       <c r="H2" s="106"/>
@@ -5544,7 +5547,7 @@
       <c r="J2" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="L2" s="207"/>
+      <c r="L2" s="206"/>
       <c r="M2" s="78"/>
       <c r="N2" s="78"/>
       <c r="O2" s="101"/>
@@ -5555,7 +5558,7 @@
         <v>76</v>
       </c>
       <c r="B3" s="6"/>
-      <c r="C3" s="234"/>
+      <c r="C3" s="233"/>
       <c r="D3" s="48"/>
       <c r="E3" s="125"/>
       <c r="F3" s="48"/>
@@ -5564,11 +5567,11 @@
       <c r="I3" s="100"/>
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
-      <c r="L3" s="205"/>
+      <c r="L3" s="204"/>
       <c r="M3" s="79"/>
       <c r="N3" s="79"/>
-      <c r="O3" s="227"/>
-      <c r="P3" s="207"/>
+      <c r="O3" s="226"/>
+      <c r="P3" s="206"/>
       <c r="Q3" s="9"/>
     </row>
     <row r="4" spans="1:18" s="4" customFormat="1" ht="15">
@@ -5577,14 +5580,14 @@
       </c>
       <c r="C4" s="104"/>
       <c r="D4" s="106"/>
-      <c r="E4" s="215"/>
+      <c r="E4" s="214"/>
       <c r="F4" s="106"/>
       <c r="G4" s="182"/>
       <c r="H4" s="101"/>
       <c r="I4" s="101"/>
       <c r="J4" s="11"/>
       <c r="K4" s="11"/>
-      <c r="L4" s="206"/>
+      <c r="L4" s="205"/>
       <c r="M4" s="112"/>
       <c r="N4" s="112"/>
       <c r="O4" s="101"/>
@@ -5596,86 +5599,86 @@
       <c r="B5" s="4"/>
       <c r="C5" s="104"/>
       <c r="D5" s="106"/>
-      <c r="E5" s="214"/>
+      <c r="E5" s="213"/>
       <c r="F5" s="106"/>
       <c r="G5" s="182"/>
       <c r="H5" s="101"/>
       <c r="I5" s="101"/>
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
-      <c r="L5" s="207"/>
+      <c r="L5" s="206"/>
       <c r="M5" s="81"/>
       <c r="N5" s="81"/>
-      <c r="O5" s="228"/>
-      <c r="P5" s="235"/>
+      <c r="O5" s="227"/>
+      <c r="P5" s="234"/>
       <c r="Q5" s="13" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="18" customHeight="1">
-      <c r="A6" s="285" t="s">
+      <c r="A6" s="282" t="s">
         <v>114</v>
       </c>
-      <c r="B6" s="285"/>
-      <c r="C6" s="285"/>
-      <c r="D6" s="285"/>
-      <c r="E6" s="285"/>
-      <c r="F6" s="285"/>
-      <c r="G6" s="285"/>
-      <c r="H6" s="285"/>
-      <c r="I6" s="285"/>
-      <c r="J6" s="285" t="s">
+      <c r="B6" s="282"/>
+      <c r="C6" s="282"/>
+      <c r="D6" s="282"/>
+      <c r="E6" s="282"/>
+      <c r="F6" s="282"/>
+      <c r="G6" s="282"/>
+      <c r="H6" s="282"/>
+      <c r="I6" s="282"/>
+      <c r="J6" s="282" t="s">
         <v>100</v>
       </c>
-      <c r="K6" s="285"/>
-      <c r="L6" s="285"/>
-      <c r="M6" s="285"/>
-      <c r="N6" s="285"/>
-      <c r="O6" s="285"/>
-      <c r="P6" s="285"/>
-      <c r="Q6" s="285"/>
+      <c r="K6" s="282"/>
+      <c r="L6" s="282"/>
+      <c r="M6" s="282"/>
+      <c r="N6" s="282"/>
+      <c r="O6" s="282"/>
+      <c r="P6" s="282"/>
+      <c r="Q6" s="282"/>
       <c r="R6" s="14"/>
     </row>
     <row r="7" spans="1:18" ht="15" customHeight="1">
-      <c r="A7" s="283" t="s">
+      <c r="A7" s="280" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="283" t="s">
+      <c r="B7" s="280" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="283" t="s">
+      <c r="C7" s="280" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="283"/>
-      <c r="E7" s="283"/>
-      <c r="F7" s="283"/>
-      <c r="G7" s="283"/>
-      <c r="H7" s="283" t="s">
+      <c r="D7" s="280"/>
+      <c r="E7" s="280"/>
+      <c r="F7" s="280"/>
+      <c r="G7" s="280"/>
+      <c r="H7" s="280" t="s">
         <v>5</v>
       </c>
-      <c r="I7" s="283" t="s">
+      <c r="I7" s="280" t="s">
         <v>6</v>
       </c>
-      <c r="J7" s="283" t="s">
+      <c r="J7" s="280" t="s">
         <v>2</v>
       </c>
-      <c r="K7" s="283" t="s">
+      <c r="K7" s="280" t="s">
         <v>3</v>
       </c>
-      <c r="L7" s="283" t="s">
+      <c r="L7" s="280" t="s">
         <v>4</v>
       </c>
-      <c r="M7" s="283"/>
-      <c r="N7" s="283"/>
-      <c r="O7" s="283"/>
-      <c r="P7" s="283"/>
-      <c r="Q7" s="283" t="s">
+      <c r="M7" s="280"/>
+      <c r="N7" s="280"/>
+      <c r="O7" s="280"/>
+      <c r="P7" s="280"/>
+      <c r="Q7" s="280" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="59.25" customHeight="1">
-      <c r="A8" s="283"/>
-      <c r="B8" s="283"/>
+      <c r="A8" s="280"/>
+      <c r="B8" s="280"/>
       <c r="C8" s="159" t="s">
         <v>69</v>
       </c>
@@ -5691,10 +5694,10 @@
       <c r="G8" s="159" t="s">
         <v>59</v>
       </c>
-      <c r="H8" s="283"/>
-      <c r="I8" s="283"/>
-      <c r="J8" s="283"/>
-      <c r="K8" s="283"/>
+      <c r="H8" s="280"/>
+      <c r="I8" s="280"/>
+      <c r="J8" s="280"/>
+      <c r="K8" s="280"/>
       <c r="L8" s="159" t="s">
         <v>69</v>
       </c>
@@ -5710,7 +5713,7 @@
       <c r="P8" s="159" t="s">
         <v>59</v>
       </c>
-      <c r="Q8" s="283"/>
+      <c r="Q8" s="280"/>
       <c r="R8" s="17"/>
     </row>
     <row r="9" spans="1:18">
@@ -5804,7 +5807,7 @@
       </c>
       <c r="C11" s="171"/>
       <c r="D11" s="195"/>
-      <c r="E11" s="216"/>
+      <c r="E11" s="215"/>
       <c r="F11" s="195"/>
       <c r="G11" s="161"/>
       <c r="H11" s="139"/>
@@ -5815,10 +5818,10 @@
       <c r="K11" s="136" t="s">
         <v>51</v>
       </c>
-      <c r="L11" s="237"/>
+      <c r="L11" s="236"/>
       <c r="M11" s="138"/>
       <c r="N11" s="138"/>
-      <c r="O11" s="226"/>
+      <c r="O11" s="225"/>
       <c r="P11" s="171"/>
       <c r="Q11" s="137"/>
       <c r="R11" s="24"/>
@@ -5832,7 +5835,7 @@
       </c>
       <c r="C12" s="171"/>
       <c r="D12" s="195"/>
-      <c r="E12" s="216"/>
+      <c r="E12" s="215"/>
       <c r="F12" s="195"/>
       <c r="G12" s="161"/>
       <c r="H12" s="139"/>
@@ -5843,160 +5846,160 @@
       <c r="K12" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="L12" s="237"/>
-      <c r="M12" s="267"/>
+      <c r="L12" s="236"/>
+      <c r="M12" s="264"/>
       <c r="N12" s="143"/>
-      <c r="O12" s="226"/>
+      <c r="O12" s="225"/>
       <c r="P12" s="171"/>
       <c r="Q12" s="137"/>
       <c r="R12" s="24"/>
     </row>
     <row r="13" spans="1:18" s="105" customFormat="1" ht="30">
-      <c r="A13" s="222">
+      <c r="A13" s="221">
         <v>1</v>
       </c>
       <c r="B13" s="140" t="s">
         <v>112</v>
       </c>
-      <c r="C13" s="280">
+      <c r="C13" s="277">
         <v>46293</v>
       </c>
-      <c r="D13" s="258">
-        <v>24</v>
-      </c>
-      <c r="E13" s="259">
-        <v>24</v>
-      </c>
-      <c r="F13" s="260">
-        <v>24</v>
-      </c>
-      <c r="G13" s="280">
+      <c r="D13" s="257">
+        <v>4</v>
+      </c>
+      <c r="E13" s="257">
+        <v>4</v>
+      </c>
+      <c r="F13" s="257">
+        <v>4</v>
+      </c>
+      <c r="G13" s="277">
         <v>46295</v>
       </c>
-      <c r="H13" s="244">
+      <c r="H13" s="243">
         <v>1</v>
       </c>
-      <c r="I13" s="244"/>
-      <c r="J13" s="222">
+      <c r="I13" s="243"/>
+      <c r="J13" s="221">
         <v>1</v>
       </c>
       <c r="K13" s="140" t="s">
         <v>109</v>
       </c>
-      <c r="L13" s="281">
+      <c r="L13" s="278">
         <v>46301</v>
       </c>
-      <c r="M13" s="258">
-        <v>8</v>
-      </c>
-      <c r="N13" s="261"/>
-      <c r="O13" s="246"/>
-      <c r="P13" s="280">
+      <c r="M13" s="257">
+        <v>1</v>
+      </c>
+      <c r="N13" s="258"/>
+      <c r="O13" s="245"/>
+      <c r="P13" s="277">
         <v>46301</v>
       </c>
-      <c r="Q13" s="247"/>
-      <c r="R13" s="248"/>
+      <c r="Q13" s="246"/>
+      <c r="R13" s="247"/>
     </row>
     <row r="14" spans="1:18" s="105" customFormat="1" ht="60">
-      <c r="A14" s="222">
+      <c r="A14" s="221">
         <v>2</v>
       </c>
       <c r="B14" s="140" t="s">
         <v>113</v>
       </c>
-      <c r="C14" s="280">
+      <c r="C14" s="277">
         <v>46293</v>
       </c>
-      <c r="D14" s="258">
-        <v>32</v>
-      </c>
-      <c r="E14" s="258">
-        <v>32</v>
-      </c>
-      <c r="F14" s="258">
-        <v>32</v>
-      </c>
-      <c r="G14" s="280">
+      <c r="D14" s="257">
+        <v>3</v>
+      </c>
+      <c r="E14" s="257">
+        <v>3</v>
+      </c>
+      <c r="F14" s="257">
+        <v>3</v>
+      </c>
+      <c r="G14" s="277">
         <v>46296</v>
       </c>
-      <c r="H14" s="244">
+      <c r="H14" s="243">
         <v>1</v>
       </c>
-      <c r="I14" s="244"/>
-      <c r="J14" s="222">
+      <c r="I14" s="243"/>
+      <c r="J14" s="221">
         <v>2</v>
       </c>
       <c r="K14" s="140" t="s">
         <v>101</v>
       </c>
-      <c r="L14" s="281">
+      <c r="L14" s="278">
         <v>46302</v>
       </c>
-      <c r="M14" s="258">
-        <v>8</v>
-      </c>
-      <c r="N14" s="261"/>
-      <c r="O14" s="246"/>
-      <c r="P14" s="280">
+      <c r="M14" s="257">
+        <v>2</v>
+      </c>
+      <c r="N14" s="258"/>
+      <c r="O14" s="245"/>
+      <c r="P14" s="277">
         <v>46302</v>
       </c>
-      <c r="Q14" s="247"/>
-      <c r="R14" s="248"/>
+      <c r="Q14" s="246"/>
+      <c r="R14" s="247"/>
     </row>
     <row r="15" spans="1:18" s="105" customFormat="1" ht="75">
-      <c r="A15" s="222">
+      <c r="A15" s="221">
         <v>3</v>
       </c>
       <c r="B15" s="140" t="s">
         <v>102</v>
       </c>
-      <c r="C15" s="280">
+      <c r="C15" s="277">
         <v>46296</v>
       </c>
-      <c r="D15" s="258">
-        <v>16</v>
-      </c>
-      <c r="E15" s="258">
-        <v>16</v>
-      </c>
-      <c r="F15" s="258">
-        <v>16</v>
-      </c>
-      <c r="G15" s="280">
+      <c r="D15" s="257">
+        <v>3</v>
+      </c>
+      <c r="E15" s="257">
+        <v>3</v>
+      </c>
+      <c r="F15" s="257">
+        <v>3</v>
+      </c>
+      <c r="G15" s="277">
         <v>46297</v>
       </c>
-      <c r="H15" s="244">
+      <c r="H15" s="243">
         <v>1</v>
       </c>
-      <c r="I15" s="244"/>
-      <c r="J15" s="222">
+      <c r="I15" s="243"/>
+      <c r="J15" s="221">
         <v>3</v>
       </c>
       <c r="K15" s="140" t="s">
         <v>110</v>
       </c>
-      <c r="L15" s="281">
+      <c r="L15" s="278">
         <v>46301</v>
       </c>
-      <c r="M15" s="258">
-        <v>8</v>
-      </c>
-      <c r="N15" s="261"/>
-      <c r="O15" s="246"/>
-      <c r="P15" s="280">
+      <c r="M15" s="257">
+        <v>2</v>
+      </c>
+      <c r="N15" s="258"/>
+      <c r="O15" s="245"/>
+      <c r="P15" s="277">
         <v>46301</v>
       </c>
-      <c r="Q15" s="247"/>
-      <c r="R15" s="248"/>
+      <c r="Q15" s="246"/>
+      <c r="R15" s="247"/>
     </row>
     <row r="16" spans="1:18" s="25" customFormat="1" ht="60">
-      <c r="A16" s="222">
+      <c r="A16" s="221">
         <v>4</v>
       </c>
       <c r="B16" s="140" t="s">
         <v>103</v>
       </c>
-      <c r="C16" s="280">
+      <c r="C16" s="277">
         <v>46294</v>
       </c>
       <c r="D16" s="108">
@@ -6008,374 +6011,374 @@
       <c r="F16" s="108">
         <v>8</v>
       </c>
-      <c r="G16" s="282">
+      <c r="G16" s="279">
         <v>46294</v>
       </c>
-      <c r="H16" s="244">
+      <c r="H16" s="243">
         <v>1</v>
       </c>
-      <c r="I16" s="222"/>
-      <c r="J16" s="222">
+      <c r="I16" s="221"/>
+      <c r="J16" s="221">
         <v>4</v>
       </c>
       <c r="K16" s="140" t="s">
         <v>104</v>
       </c>
-      <c r="L16" s="281">
+      <c r="L16" s="278">
         <v>46302</v>
       </c>
-      <c r="M16" s="258">
-        <v>16</v>
-      </c>
-      <c r="N16" s="261"/>
-      <c r="O16" s="222"/>
-      <c r="P16" s="280">
+      <c r="M16" s="257">
+        <v>4</v>
+      </c>
+      <c r="N16" s="258"/>
+      <c r="O16" s="221"/>
+      <c r="P16" s="277">
         <v>46303</v>
       </c>
-      <c r="Q16" s="247"/>
-      <c r="R16" s="249"/>
+      <c r="Q16" s="246"/>
+      <c r="R16" s="248"/>
     </row>
     <row r="17" spans="1:21" s="105" customFormat="1" ht="60">
-      <c r="A17" s="251">
+      <c r="A17" s="250">
         <v>5</v>
       </c>
       <c r="B17" s="140" t="s">
         <v>105</v>
       </c>
-      <c r="C17" s="280">
+      <c r="C17" s="277">
         <v>46295</v>
       </c>
-      <c r="D17" s="258">
-        <v>16</v>
-      </c>
-      <c r="E17" s="258">
-        <v>16</v>
-      </c>
-      <c r="F17" s="258">
-        <v>16</v>
-      </c>
-      <c r="G17" s="280">
+      <c r="D17" s="257">
+        <v>2</v>
+      </c>
+      <c r="E17" s="257">
+        <v>2</v>
+      </c>
+      <c r="F17" s="257">
+        <v>2</v>
+      </c>
+      <c r="G17" s="277">
         <v>46296</v>
       </c>
-      <c r="H17" s="244">
+      <c r="H17" s="243">
         <v>1</v>
       </c>
-      <c r="I17" s="244"/>
-      <c r="J17" s="251">
+      <c r="I17" s="243"/>
+      <c r="J17" s="250">
         <v>5</v>
       </c>
       <c r="K17" s="140" t="s">
         <v>106</v>
       </c>
-      <c r="L17" s="280">
+      <c r="L17" s="277">
         <v>46303</v>
       </c>
       <c r="M17" s="181">
-        <v>16</v>
-      </c>
-      <c r="N17" s="261"/>
-      <c r="O17" s="246"/>
-      <c r="P17" s="280">
+        <v>2</v>
+      </c>
+      <c r="N17" s="258"/>
+      <c r="O17" s="245"/>
+      <c r="P17" s="277">
         <v>46304</v>
       </c>
-      <c r="Q17" s="252"/>
-      <c r="R17" s="249"/>
+      <c r="Q17" s="251"/>
+      <c r="R17" s="248"/>
     </row>
     <row r="18" spans="1:21" s="105" customFormat="1" ht="60">
-      <c r="A18" s="251">
+      <c r="A18" s="250">
         <v>6</v>
       </c>
       <c r="B18" s="140" t="s">
         <v>107</v>
       </c>
-      <c r="C18" s="280">
+      <c r="C18" s="277">
         <v>46295</v>
       </c>
-      <c r="D18" s="261">
-        <v>16</v>
-      </c>
-      <c r="E18" s="261">
-        <v>16</v>
-      </c>
-      <c r="F18" s="261">
-        <v>16</v>
-      </c>
-      <c r="G18" s="280">
+      <c r="D18" s="258">
+        <v>4</v>
+      </c>
+      <c r="E18" s="258">
+        <v>4</v>
+      </c>
+      <c r="F18" s="258">
+        <v>4</v>
+      </c>
+      <c r="G18" s="277">
         <v>46296</v>
       </c>
-      <c r="H18" s="244">
+      <c r="H18" s="243">
         <v>1</v>
       </c>
-      <c r="I18" s="244"/>
-      <c r="J18" s="251">
+      <c r="I18" s="243"/>
+      <c r="J18" s="250">
         <v>6</v>
       </c>
       <c r="K18" s="140" t="s">
         <v>111</v>
       </c>
-      <c r="L18" s="280">
+      <c r="L18" s="277">
         <v>46304</v>
       </c>
       <c r="M18" s="108">
         <v>8</v>
       </c>
-      <c r="N18" s="261"/>
-      <c r="O18" s="246"/>
-      <c r="P18" s="280">
+      <c r="N18" s="258"/>
+      <c r="O18" s="245"/>
+      <c r="P18" s="277">
         <v>46304</v>
       </c>
-      <c r="Q18" s="252"/>
-      <c r="R18" s="249"/>
+      <c r="Q18" s="251"/>
+      <c r="R18" s="248"/>
     </row>
     <row r="19" spans="1:21" s="105" customFormat="1" ht="60">
-      <c r="A19" s="251">
+      <c r="A19" s="250">
         <v>7</v>
       </c>
       <c r="B19" s="140" t="s">
         <v>108</v>
       </c>
-      <c r="C19" s="280">
+      <c r="C19" s="277">
         <v>46297</v>
       </c>
-      <c r="D19" s="261">
-        <v>8</v>
-      </c>
-      <c r="E19" s="261">
-        <v>8</v>
-      </c>
-      <c r="F19" s="261">
-        <v>8</v>
-      </c>
-      <c r="G19" s="280">
+      <c r="D19" s="258">
+        <v>4</v>
+      </c>
+      <c r="E19" s="258">
+        <v>2</v>
+      </c>
+      <c r="F19" s="258">
+        <v>2</v>
+      </c>
+      <c r="G19" s="277">
         <v>46297</v>
       </c>
-      <c r="H19" s="244">
+      <c r="H19" s="243">
         <v>0.5</v>
       </c>
-      <c r="I19" s="244"/>
-      <c r="J19" s="251">
+      <c r="I19" s="243"/>
+      <c r="J19" s="250">
         <v>7</v>
       </c>
       <c r="K19" s="140" t="s">
         <v>108</v>
       </c>
-      <c r="L19" s="280">
+      <c r="L19" s="277">
         <v>46297</v>
       </c>
       <c r="M19" s="108">
-        <v>56</v>
-      </c>
-      <c r="N19" s="258">
-        <v>1</v>
-      </c>
-      <c r="O19" s="246"/>
-      <c r="P19" s="280">
+        <v>4</v>
+      </c>
+      <c r="N19" s="257">
+        <v>2</v>
+      </c>
+      <c r="O19" s="245"/>
+      <c r="P19" s="277">
         <v>46303</v>
       </c>
-      <c r="Q19" s="252"/>
-      <c r="R19" s="249"/>
+      <c r="Q19" s="251"/>
+      <c r="R19" s="248"/>
     </row>
     <row r="20" spans="1:21" s="105" customFormat="1" ht="15">
-      <c r="A20" s="251"/>
+      <c r="A20" s="250"/>
       <c r="B20" s="140"/>
-      <c r="C20" s="242"/>
-      <c r="D20" s="261"/>
-      <c r="E20" s="261"/>
-      <c r="F20" s="262"/>
-      <c r="G20" s="242"/>
-      <c r="H20" s="244"/>
-      <c r="I20" s="244"/>
-      <c r="J20" s="251">
+      <c r="C20" s="241"/>
+      <c r="D20" s="258"/>
+      <c r="E20" s="258"/>
+      <c r="F20" s="259"/>
+      <c r="G20" s="241"/>
+      <c r="H20" s="243"/>
+      <c r="I20" s="243"/>
+      <c r="J20" s="250">
         <v>8</v>
       </c>
       <c r="K20" s="140" t="s">
         <v>115</v>
       </c>
-      <c r="L20" s="280">
+      <c r="L20" s="277">
         <v>46304</v>
       </c>
       <c r="M20" s="108">
         <v>4</v>
       </c>
-      <c r="N20" s="261"/>
-      <c r="O20" s="246"/>
-      <c r="P20" s="280">
+      <c r="N20" s="258"/>
+      <c r="O20" s="245"/>
+      <c r="P20" s="277">
         <v>46304</v>
       </c>
-      <c r="Q20" s="252"/>
-      <c r="R20" s="249"/>
+      <c r="Q20" s="251"/>
+      <c r="R20" s="248"/>
     </row>
     <row r="21" spans="1:21" s="25" customFormat="1" ht="15">
-      <c r="A21" s="268" t="s">
+      <c r="A21" s="265" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="269" t="s">
+      <c r="B21" s="266" t="s">
         <v>98</v>
       </c>
-      <c r="C21" s="270"/>
-      <c r="D21" s="271"/>
-      <c r="E21" s="272"/>
-      <c r="F21" s="271"/>
-      <c r="G21" s="273"/>
-      <c r="H21" s="271"/>
-      <c r="I21" s="271"/>
-      <c r="J21" s="268" t="s">
+      <c r="C21" s="267"/>
+      <c r="D21" s="268"/>
+      <c r="E21" s="269"/>
+      <c r="F21" s="268"/>
+      <c r="G21" s="270"/>
+      <c r="H21" s="268"/>
+      <c r="I21" s="268"/>
+      <c r="J21" s="265" t="s">
         <v>25</v>
       </c>
-      <c r="K21" s="269" t="s">
+      <c r="K21" s="266" t="s">
         <v>98</v>
       </c>
-      <c r="L21" s="274"/>
-      <c r="M21" s="275"/>
-      <c r="N21" s="276"/>
-      <c r="O21" s="277"/>
-      <c r="P21" s="278"/>
-      <c r="Q21" s="279"/>
+      <c r="L21" s="271"/>
+      <c r="M21" s="272"/>
+      <c r="N21" s="273"/>
+      <c r="O21" s="274"/>
+      <c r="P21" s="275"/>
+      <c r="Q21" s="276"/>
       <c r="R21" s="24"/>
     </row>
     <row r="22" spans="1:21" s="105" customFormat="1" ht="45">
-      <c r="A22" s="222">
+      <c r="A22" s="221">
         <v>1</v>
       </c>
       <c r="B22" s="140" t="s">
         <v>121</v>
       </c>
-      <c r="C22" s="280">
+      <c r="C22" s="277">
         <v>46293</v>
       </c>
-      <c r="D22" s="261">
-        <v>256</v>
-      </c>
-      <c r="E22" s="261">
-        <v>256</v>
-      </c>
-      <c r="F22" s="222">
-        <v>256</v>
-      </c>
-      <c r="G22" s="282">
+      <c r="D22" s="258">
+        <v>1</v>
+      </c>
+      <c r="E22" s="258">
+        <v>1</v>
+      </c>
+      <c r="F22" s="221">
+        <v>1</v>
+      </c>
+      <c r="G22" s="279">
         <v>46324</v>
       </c>
-      <c r="H22" s="244">
+      <c r="H22" s="243">
         <v>1</v>
       </c>
-      <c r="I22" s="244"/>
-      <c r="J22" s="222">
+      <c r="I22" s="243"/>
+      <c r="J22" s="221">
         <v>1</v>
       </c>
       <c r="K22" s="140" t="s">
         <v>120</v>
       </c>
-      <c r="L22" s="281">
+      <c r="L22" s="278">
         <v>46301</v>
       </c>
-      <c r="M22" s="261">
-        <v>128</v>
-      </c>
-      <c r="N22" s="261">
+      <c r="M22" s="258">
+        <v>4</v>
+      </c>
+      <c r="N22" s="258">
         <v>0</v>
       </c>
-      <c r="O22" s="222"/>
-      <c r="P22" s="280">
-        <v>46316</v>
-      </c>
-      <c r="Q22" s="247"/>
-      <c r="R22" s="248"/>
+      <c r="O22" s="221"/>
+      <c r="P22" s="277">
+        <v>46304</v>
+      </c>
+      <c r="Q22" s="246"/>
+      <c r="R22" s="247"/>
     </row>
     <row r="23" spans="1:21" s="105" customFormat="1" ht="45">
-      <c r="A23" s="222">
+      <c r="A23" s="221">
         <v>2</v>
       </c>
       <c r="B23" s="140" t="s">
         <v>116</v>
       </c>
-      <c r="C23" s="280">
+      <c r="C23" s="277">
         <v>46294</v>
       </c>
-      <c r="D23" s="261">
-        <v>32</v>
-      </c>
-      <c r="E23" s="261">
-        <v>32</v>
-      </c>
-      <c r="F23" s="222">
-        <v>32</v>
-      </c>
-      <c r="G23" s="282">
+      <c r="D23" s="258">
+        <v>4</v>
+      </c>
+      <c r="E23" s="258">
+        <v>4</v>
+      </c>
+      <c r="F23" s="221">
+        <v>4</v>
+      </c>
+      <c r="G23" s="279">
         <v>46297</v>
       </c>
-      <c r="H23" s="244">
+      <c r="H23" s="243">
         <v>1</v>
       </c>
-      <c r="I23" s="244"/>
-      <c r="J23" s="222">
+      <c r="I23" s="243"/>
+      <c r="J23" s="221">
         <v>2</v>
       </c>
       <c r="K23" s="140" t="s">
         <v>117</v>
       </c>
-      <c r="L23" s="281">
+      <c r="L23" s="278">
         <v>46302</v>
       </c>
-      <c r="M23" s="261">
-        <v>32</v>
-      </c>
-      <c r="N23" s="261">
+      <c r="M23" s="258">
+        <v>4</v>
+      </c>
+      <c r="N23" s="258">
         <v>0</v>
       </c>
-      <c r="O23" s="222"/>
-      <c r="P23" s="242">
+      <c r="O23" s="221"/>
+      <c r="P23" s="241">
         <v>46305</v>
       </c>
-      <c r="Q23" s="247"/>
-      <c r="R23" s="248"/>
+      <c r="Q23" s="246"/>
+      <c r="R23" s="247"/>
     </row>
     <row r="24" spans="1:21" s="105" customFormat="1" ht="45">
-      <c r="A24" s="222">
+      <c r="A24" s="221">
         <v>3</v>
       </c>
       <c r="B24" s="140" t="s">
         <v>118</v>
       </c>
-      <c r="C24" s="280">
+      <c r="C24" s="277">
         <v>46297</v>
       </c>
-      <c r="D24" s="261">
-        <v>48</v>
-      </c>
-      <c r="E24" s="261">
-        <v>48</v>
-      </c>
-      <c r="F24" s="222">
-        <v>48</v>
-      </c>
-      <c r="G24" s="282">
+      <c r="D24" s="258">
+        <v>8</v>
+      </c>
+      <c r="E24" s="258">
+        <v>8</v>
+      </c>
+      <c r="F24" s="221">
+        <v>8</v>
+      </c>
+      <c r="G24" s="279">
         <v>46302</v>
       </c>
-      <c r="H24" s="244">
+      <c r="H24" s="243">
         <v>0</v>
       </c>
-      <c r="I24" s="244"/>
-      <c r="J24" s="222">
+      <c r="I24" s="243"/>
+      <c r="J24" s="221">
         <v>3</v>
       </c>
       <c r="K24" s="140" t="s">
         <v>118</v>
       </c>
-      <c r="L24" s="280">
+      <c r="L24" s="277">
         <v>46297</v>
       </c>
-      <c r="M24" s="261">
-        <v>48</v>
-      </c>
-      <c r="N24" s="261">
+      <c r="M24" s="258">
+        <v>8</v>
+      </c>
+      <c r="N24" s="258">
         <v>0</v>
       </c>
-      <c r="O24" s="222"/>
-      <c r="P24" s="280">
+      <c r="O24" s="221"/>
+      <c r="P24" s="277">
         <v>46302</v>
       </c>
-      <c r="Q24" s="247"/>
-      <c r="R24" s="248"/>
+      <c r="Q24" s="246"/>
+      <c r="R24" s="247"/>
     </row>
     <row r="25" spans="1:21" s="25" customFormat="1" ht="15" hidden="1">
       <c r="A25" s="135" t="s">
@@ -6385,8 +6388,8 @@
         <v>53</v>
       </c>
       <c r="C25" s="171"/>
-      <c r="D25" s="264"/>
-      <c r="E25" s="266"/>
+      <c r="D25" s="261"/>
+      <c r="E25" s="263"/>
       <c r="F25" s="139"/>
       <c r="G25" s="161"/>
       <c r="H25" s="139"/>
@@ -6397,10 +6400,10 @@
       <c r="K25" s="136" t="s">
         <v>53</v>
       </c>
-      <c r="L25" s="237"/>
-      <c r="M25" s="263"/>
-      <c r="N25" s="264"/>
-      <c r="O25" s="226"/>
+      <c r="L25" s="236"/>
+      <c r="M25" s="260"/>
+      <c r="N25" s="261"/>
+      <c r="O25" s="225"/>
       <c r="P25" s="171"/>
       <c r="Q25" s="137"/>
       <c r="R25" s="24"/>
@@ -6409,47 +6412,47 @@
       <c r="A26" s="135"/>
       <c r="B26" s="136"/>
       <c r="C26" s="171"/>
-      <c r="D26" s="264"/>
-      <c r="E26" s="266"/>
+      <c r="D26" s="261"/>
+      <c r="E26" s="263"/>
       <c r="F26" s="139"/>
       <c r="G26" s="161"/>
       <c r="H26" s="139"/>
       <c r="I26" s="139"/>
-      <c r="J26" s="222">
+      <c r="J26" s="221">
         <v>4</v>
       </c>
       <c r="K26" s="140" t="s">
         <v>119</v>
       </c>
-      <c r="L26" s="245">
+      <c r="L26" s="244">
         <v>46244</v>
       </c>
-      <c r="M26" s="261">
+      <c r="M26" s="258">
         <v>4</v>
       </c>
-      <c r="N26" s="264"/>
-      <c r="O26" s="226"/>
-      <c r="P26" s="242">
+      <c r="N26" s="261"/>
+      <c r="O26" s="225"/>
+      <c r="P26" s="241">
         <v>46366</v>
       </c>
       <c r="Q26" s="137"/>
       <c r="R26" s="24"/>
     </row>
     <row r="27" spans="1:21" s="31" customFormat="1" ht="15">
-      <c r="A27" s="222"/>
+      <c r="A27" s="221"/>
       <c r="B27" s="140"/>
       <c r="C27" s="148"/>
-      <c r="D27" s="264"/>
-      <c r="E27" s="264"/>
+      <c r="D27" s="261"/>
+      <c r="E27" s="261"/>
       <c r="F27" s="146"/>
       <c r="G27" s="165"/>
       <c r="H27" s="185"/>
       <c r="I27" s="185"/>
-      <c r="J27" s="222"/>
+      <c r="J27" s="221"/>
       <c r="K27" s="140"/>
-      <c r="L27" s="208"/>
-      <c r="M27" s="265"/>
-      <c r="N27" s="264"/>
+      <c r="L27" s="207"/>
+      <c r="M27" s="262"/>
+      <c r="N27" s="261"/>
       <c r="O27" s="146"/>
       <c r="P27" s="148"/>
       <c r="Q27" s="40"/>
@@ -6467,7 +6470,7 @@
       <c r="I28" s="185"/>
       <c r="J28" s="108"/>
       <c r="K28" s="147"/>
-      <c r="L28" s="208"/>
+      <c r="L28" s="207"/>
       <c r="M28" s="142"/>
       <c r="N28" s="149"/>
       <c r="O28" s="146"/>
@@ -6487,7 +6490,7 @@
       <c r="I29" s="185"/>
       <c r="J29" s="108"/>
       <c r="K29" s="147"/>
-      <c r="L29" s="208"/>
+      <c r="L29" s="207"/>
       <c r="M29" s="142"/>
       <c r="N29" s="149"/>
       <c r="O29" s="146"/>
@@ -6507,7 +6510,7 @@
       <c r="I30" s="185"/>
       <c r="J30" s="108"/>
       <c r="K30" s="147"/>
-      <c r="L30" s="208"/>
+      <c r="L30" s="207"/>
       <c r="M30" s="142"/>
       <c r="N30" s="149"/>
       <c r="O30" s="146"/>
@@ -6524,7 +6527,7 @@
       </c>
       <c r="C31" s="171"/>
       <c r="D31" s="195"/>
-      <c r="E31" s="216"/>
+      <c r="E31" s="215"/>
       <c r="F31" s="195"/>
       <c r="G31" s="161"/>
       <c r="H31" s="139"/>
@@ -6535,10 +6538,10 @@
       <c r="K31" s="136" t="s">
         <v>54</v>
       </c>
-      <c r="L31" s="237"/>
+      <c r="L31" s="236"/>
       <c r="M31" s="138"/>
       <c r="N31" s="143"/>
-      <c r="O31" s="226"/>
+      <c r="O31" s="225"/>
       <c r="P31" s="171"/>
       <c r="Q31" s="137"/>
       <c r="R31" s="24"/>
@@ -6554,7 +6557,7 @@
       </c>
       <c r="C32" s="171"/>
       <c r="D32" s="195"/>
-      <c r="E32" s="216"/>
+      <c r="E32" s="215"/>
       <c r="F32" s="195"/>
       <c r="G32" s="161"/>
       <c r="H32" s="139"/>
@@ -6565,10 +6568,10 @@
       <c r="K32" s="136" t="s">
         <v>74</v>
       </c>
-      <c r="L32" s="237"/>
+      <c r="L32" s="236"/>
       <c r="M32" s="138"/>
       <c r="N32" s="143"/>
-      <c r="O32" s="226"/>
+      <c r="O32" s="225"/>
       <c r="P32" s="171"/>
       <c r="Q32" s="137"/>
       <c r="R32" s="24"/>
@@ -6594,10 +6597,10 @@
       <c r="K33" s="151" t="s">
         <v>72</v>
       </c>
-      <c r="L33" s="238"/>
+      <c r="L33" s="237"/>
       <c r="M33" s="155"/>
       <c r="N33" s="156"/>
-      <c r="O33" s="210"/>
+      <c r="O33" s="209"/>
       <c r="P33" s="193"/>
       <c r="Q33" s="157"/>
       <c r="R33" s="118"/>
@@ -6618,10 +6621,10 @@
       <c r="I34" s="175"/>
       <c r="J34" s="170"/>
       <c r="K34" s="136"/>
-      <c r="L34" s="237"/>
+      <c r="L34" s="236"/>
       <c r="M34" s="138"/>
       <c r="N34" s="176"/>
-      <c r="O34" s="211"/>
+      <c r="O34" s="210"/>
       <c r="P34" s="194"/>
       <c r="Q34" s="158"/>
       <c r="R34" s="24"/>
@@ -6638,7 +6641,7 @@
       <c r="I35" s="185"/>
       <c r="J35" s="107"/>
       <c r="K35" s="140"/>
-      <c r="L35" s="208"/>
+      <c r="L35" s="207"/>
       <c r="M35" s="87"/>
       <c r="N35" s="143"/>
       <c r="O35" s="144"/>
@@ -6658,10 +6661,10 @@
       <c r="I36" s="175"/>
       <c r="J36" s="170"/>
       <c r="K36" s="136"/>
-      <c r="L36" s="237"/>
+      <c r="L36" s="236"/>
       <c r="M36" s="138"/>
       <c r="N36" s="176"/>
-      <c r="O36" s="211"/>
+      <c r="O36" s="210"/>
       <c r="P36" s="194"/>
       <c r="Q36" s="158"/>
       <c r="R36" s="24"/>
@@ -6678,9 +6681,9 @@
       <c r="I37" s="144"/>
       <c r="J37" s="164"/>
       <c r="K37" s="147"/>
-      <c r="L37" s="229"/>
-      <c r="M37" s="230"/>
-      <c r="N37" s="225"/>
+      <c r="L37" s="228"/>
+      <c r="M37" s="229"/>
+      <c r="N37" s="224"/>
       <c r="O37" s="144"/>
       <c r="P37" s="192"/>
       <c r="Q37" s="129"/>
@@ -6698,7 +6701,7 @@
       <c r="I38" s="163"/>
       <c r="J38" s="107"/>
       <c r="K38" s="140"/>
-      <c r="L38" s="208"/>
+      <c r="L38" s="207"/>
       <c r="M38" s="121"/>
       <c r="N38" s="143"/>
       <c r="O38" s="144"/>
@@ -6715,7 +6718,7 @@
       </c>
       <c r="C39" s="167"/>
       <c r="D39" s="199"/>
-      <c r="E39" s="217"/>
+      <c r="E39" s="216"/>
       <c r="F39" s="199"/>
       <c r="G39" s="178"/>
       <c r="H39" s="150"/>
@@ -6726,7 +6729,7 @@
       <c r="K39" s="151" t="s">
         <v>73</v>
       </c>
-      <c r="L39" s="238"/>
+      <c r="L39" s="237"/>
       <c r="M39" s="155"/>
       <c r="N39" s="180"/>
       <c r="O39" s="154"/>
@@ -6735,40 +6738,40 @@
       <c r="R39" s="118"/>
     </row>
     <row r="40" spans="1:18" s="105" customFormat="1" ht="15">
-      <c r="A40" s="222"/>
+      <c r="A40" s="221"/>
       <c r="B40" s="140"/>
-      <c r="C40" s="242"/>
-      <c r="D40" s="250"/>
-      <c r="E40" s="253"/>
-      <c r="F40" s="243"/>
-      <c r="G40" s="254"/>
-      <c r="H40" s="244"/>
-      <c r="I40" s="244"/>
-      <c r="J40" s="222"/>
+      <c r="C40" s="241"/>
+      <c r="D40" s="249"/>
+      <c r="E40" s="252"/>
+      <c r="F40" s="242"/>
+      <c r="G40" s="253"/>
+      <c r="H40" s="243"/>
+      <c r="I40" s="243"/>
+      <c r="J40" s="221"/>
       <c r="K40" s="140"/>
-      <c r="L40" s="255"/>
-      <c r="M40" s="256"/>
-      <c r="N40" s="257"/>
-      <c r="O40" s="222"/>
-      <c r="P40" s="242"/>
-      <c r="Q40" s="247"/>
-      <c r="R40" s="248"/>
+      <c r="L40" s="254"/>
+      <c r="M40" s="255"/>
+      <c r="N40" s="256"/>
+      <c r="O40" s="221"/>
+      <c r="P40" s="241"/>
+      <c r="Q40" s="246"/>
+      <c r="R40" s="247"/>
     </row>
     <row r="41" spans="1:18" s="31" customFormat="1" ht="15">
-      <c r="A41" s="222"/>
+      <c r="A41" s="221"/>
       <c r="B41" s="140"/>
       <c r="C41" s="148"/>
       <c r="D41" s="200"/>
-      <c r="E41" s="223"/>
+      <c r="E41" s="222"/>
       <c r="F41" s="200"/>
       <c r="G41" s="120"/>
       <c r="H41" s="41"/>
       <c r="I41" s="41"/>
-      <c r="J41" s="222"/>
+      <c r="J41" s="221"/>
       <c r="K41" s="140"/>
-      <c r="L41" s="229"/>
-      <c r="M41" s="224"/>
-      <c r="N41" s="225"/>
+      <c r="L41" s="228"/>
+      <c r="M41" s="223"/>
+      <c r="N41" s="224"/>
       <c r="O41" s="146"/>
       <c r="P41" s="148"/>
       <c r="Q41" s="40"/>
@@ -6781,9 +6784,10 @@
       </c>
       <c r="C42" s="146"/>
       <c r="D42" s="41"/>
-      <c r="E42" s="209"/>
+      <c r="E42" s="208"/>
       <c r="F42" s="200">
-        <v>29</v>
+        <f>SUM(F13:F19,F22,F23,F24)</f>
+        <v>39</v>
       </c>
       <c r="G42" s="120"/>
       <c r="H42" s="41"/>
@@ -6792,7 +6796,7 @@
       <c r="K42" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="L42" s="208"/>
+      <c r="L42" s="207"/>
       <c r="M42" s="87"/>
       <c r="N42" s="87"/>
       <c r="O42" s="141">
@@ -6810,7 +6814,7 @@
       </c>
       <c r="C43" s="148"/>
       <c r="D43" s="41"/>
-      <c r="E43" s="209"/>
+      <c r="E43" s="208"/>
       <c r="F43" s="200">
         <v>44</v>
       </c>
@@ -6821,7 +6825,7 @@
       <c r="K43" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="L43" s="208"/>
+      <c r="L43" s="207"/>
       <c r="M43" s="87"/>
       <c r="N43" s="87"/>
       <c r="O43" s="141">
@@ -6838,9 +6842,10 @@
       </c>
       <c r="C44" s="185"/>
       <c r="D44" s="41"/>
-      <c r="E44" s="209"/>
-      <c r="F44" s="201">
-        <v>0.65910000000000002</v>
+      <c r="E44" s="208"/>
+      <c r="F44" s="295">
+        <f>(F42/F43)</f>
+        <v>0.88636363636363635</v>
       </c>
       <c r="G44" s="120"/>
       <c r="H44" s="41"/>
@@ -6849,7 +6854,7 @@
       <c r="K44" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="L44" s="208"/>
+      <c r="L44" s="207"/>
       <c r="M44" s="87"/>
       <c r="N44" s="87"/>
       <c r="O44" s="185">
@@ -6863,7 +6868,7 @@
     <row r="45" spans="1:18" ht="15" hidden="1">
       <c r="A45" s="106"/>
       <c r="B45" s="10"/>
-      <c r="C45" s="234"/>
+      <c r="C45" s="233"/>
       <c r="D45" s="48"/>
       <c r="E45" s="125"/>
       <c r="F45" s="48"/>
@@ -6872,18 +6877,18 @@
       <c r="I45" s="48"/>
       <c r="J45" s="10"/>
       <c r="K45" s="10"/>
-      <c r="L45" s="205"/>
+      <c r="L45" s="204"/>
       <c r="M45" s="88"/>
       <c r="N45" s="88"/>
       <c r="O45" s="100"/>
-      <c r="P45" s="234"/>
+      <c r="P45" s="233"/>
       <c r="Q45" s="10"/>
       <c r="R45" s="45"/>
     </row>
     <row r="46" spans="1:18" ht="8.25" customHeight="1">
       <c r="A46" s="106"/>
       <c r="B46" s="10"/>
-      <c r="C46" s="234"/>
+      <c r="C46" s="233"/>
       <c r="D46" s="48"/>
       <c r="E46" s="125"/>
       <c r="F46" s="48"/>
@@ -6892,17 +6897,17 @@
       <c r="I46" s="48"/>
       <c r="J46" s="10"/>
       <c r="K46" s="10"/>
-      <c r="L46" s="205"/>
+      <c r="L46" s="204"/>
       <c r="M46" s="88"/>
       <c r="N46" s="88"/>
       <c r="O46" s="100"/>
-      <c r="P46" s="234"/>
+      <c r="P46" s="233"/>
       <c r="Q46" s="10"/>
       <c r="R46" s="45"/>
     </row>
     <row r="47" spans="1:18" s="46" customFormat="1" ht="15.75" customHeight="1">
       <c r="B47" s="47"/>
-      <c r="C47" s="233"/>
+      <c r="C47" s="232"/>
       <c r="D47" s="47"/>
       <c r="E47" s="124"/>
       <c r="F47" s="47"/>
@@ -6911,19 +6916,19 @@
       <c r="I47" s="47"/>
       <c r="J47" s="47"/>
       <c r="K47" s="47"/>
-      <c r="L47" s="239" t="s">
+      <c r="L47" s="238" t="s">
         <v>29</v>
       </c>
       <c r="M47" s="89"/>
       <c r="N47" s="98"/>
-      <c r="O47" s="204"/>
-      <c r="P47" s="233"/>
+      <c r="O47" s="203"/>
+      <c r="P47" s="232"/>
       <c r="Q47" s="47"/>
       <c r="R47" s="47"/>
     </row>
     <row r="48" spans="1:18" s="45" customFormat="1" ht="14.25">
       <c r="A48" s="48"/>
-      <c r="C48" s="234"/>
+      <c r="C48" s="233"/>
       <c r="D48" s="48"/>
       <c r="E48" s="125"/>
       <c r="F48" s="48" t="s">
@@ -6934,19 +6939,19 @@
       <c r="I48" s="48"/>
       <c r="J48" s="10"/>
       <c r="K48" s="10"/>
-      <c r="L48" s="205" t="s">
+      <c r="L48" s="204" t="s">
         <v>31</v>
       </c>
       <c r="M48" s="90"/>
       <c r="N48" s="88"/>
       <c r="O48" s="100"/>
-      <c r="P48" s="234"/>
+      <c r="P48" s="233"/>
       <c r="Q48" s="10"/>
     </row>
     <row r="49" spans="1:17" s="45" customFormat="1" ht="13.5" customHeight="1">
       <c r="A49" s="48"/>
       <c r="B49" s="48"/>
-      <c r="C49" s="234"/>
+      <c r="C49" s="233"/>
       <c r="D49" s="48"/>
       <c r="E49" s="125"/>
       <c r="F49" s="48"/>
@@ -6955,11 +6960,11 @@
       <c r="I49" s="48"/>
       <c r="J49" s="10"/>
       <c r="K49" s="10"/>
-      <c r="L49" s="205"/>
+      <c r="L49" s="204"/>
       <c r="M49" s="90"/>
       <c r="N49" s="88"/>
       <c r="O49" s="100"/>
-      <c r="P49" s="234"/>
+      <c r="P49" s="233"/>
       <c r="Q49" s="10"/>
     </row>
     <row r="50" spans="1:17" s="49" customFormat="1" ht="15.75">
@@ -6967,32 +6972,32 @@
       <c r="B50" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="C50" s="231"/>
-      <c r="D50" s="218"/>
-      <c r="E50" s="219"/>
+      <c r="C50" s="230"/>
+      <c r="D50" s="217"/>
+      <c r="E50" s="218"/>
       <c r="F50" s="103"/>
       <c r="G50" s="126"/>
       <c r="H50" s="103"/>
       <c r="I50" s="103"/>
-      <c r="L50" s="240"/>
+      <c r="L50" s="239"/>
       <c r="M50" s="91"/>
       <c r="N50" s="99"/>
       <c r="O50" s="187"/>
-      <c r="P50" s="231"/>
+      <c r="P50" s="230"/>
     </row>
     <row r="51" spans="1:17" s="4" customFormat="1" ht="15">
       <c r="A51" s="106"/>
-      <c r="B51" s="202" t="s">
+      <c r="B51" s="201" t="s">
         <v>33</v>
       </c>
       <c r="C51" s="104"/>
-      <c r="D51" s="220"/>
-      <c r="E51" s="214"/>
+      <c r="D51" s="219"/>
+      <c r="E51" s="213"/>
       <c r="F51" s="106"/>
       <c r="G51" s="111"/>
       <c r="H51" s="106"/>
       <c r="I51" s="106"/>
-      <c r="L51" s="207"/>
+      <c r="L51" s="206"/>
       <c r="M51" s="186"/>
       <c r="N51" s="78"/>
       <c r="O51" s="101"/>
@@ -7002,35 +7007,35 @@
       <c r="B52" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="D52" s="212"/>
+      <c r="D52" s="211"/>
       <c r="M52" s="92"/>
     </row>
     <row r="53" spans="1:17">
       <c r="B53" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="D53" s="212"/>
+      <c r="D53" s="211"/>
       <c r="M53" s="92"/>
     </row>
     <row r="54" spans="1:17">
       <c r="B54" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="D54" s="212"/>
+      <c r="D54" s="211"/>
       <c r="M54" s="92"/>
     </row>
     <row r="55" spans="1:17">
       <c r="B55" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="D55" s="212"/>
+      <c r="D55" s="211"/>
       <c r="M55" s="92"/>
     </row>
     <row r="56" spans="1:17">
       <c r="B56" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="D56" s="212"/>
+      <c r="D56" s="211"/>
       <c r="M56" s="92"/>
     </row>
     <row r="57" spans="1:17">
@@ -7038,67 +7043,67 @@
         <f>'[1]KHTuan BDH'!A31</f>
         <v>+ Fonts chữ sử dụng cho phần nội dung: Times New Roman (Cỡ chữ 10~12).</v>
       </c>
-      <c r="D57" s="212"/>
+      <c r="D57" s="211"/>
       <c r="M57" s="92"/>
     </row>
     <row r="58" spans="1:17">
       <c r="B58" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="C58" s="232"/>
+      <c r="C58" s="231"/>
       <c r="D58" s="128"/>
-      <c r="E58" s="221"/>
+      <c r="E58" s="220"/>
       <c r="F58" s="128"/>
       <c r="G58" s="127"/>
       <c r="H58" s="128"/>
       <c r="I58" s="128"/>
       <c r="J58" s="56"/>
       <c r="K58" s="56"/>
-      <c r="L58" s="241"/>
+      <c r="L58" s="240"/>
       <c r="M58" s="93"/>
       <c r="N58" s="93"/>
       <c r="O58" s="189"/>
-      <c r="P58" s="232"/>
+      <c r="P58" s="231"/>
       <c r="Q58" s="57"/>
     </row>
     <row r="59" spans="1:17">
-      <c r="B59" s="284" t="s">
+      <c r="B59" s="281" t="s">
         <v>82</v>
       </c>
-      <c r="C59" s="284"/>
-      <c r="D59" s="284"/>
-      <c r="E59" s="284"/>
-      <c r="F59" s="284"/>
-      <c r="G59" s="284"/>
-      <c r="H59" s="284"/>
-      <c r="I59" s="284"/>
-      <c r="J59" s="284"/>
-      <c r="K59" s="284"/>
-      <c r="L59" s="284"/>
-      <c r="M59" s="284"/>
-      <c r="N59" s="284"/>
-      <c r="O59" s="284"/>
-      <c r="P59" s="284"/>
+      <c r="C59" s="281"/>
+      <c r="D59" s="281"/>
+      <c r="E59" s="281"/>
+      <c r="F59" s="281"/>
+      <c r="G59" s="281"/>
+      <c r="H59" s="281"/>
+      <c r="I59" s="281"/>
+      <c r="J59" s="281"/>
+      <c r="K59" s="281"/>
+      <c r="L59" s="281"/>
+      <c r="M59" s="281"/>
+      <c r="N59" s="281"/>
+      <c r="O59" s="281"/>
+      <c r="P59" s="281"/>
       <c r="Q59" s="57"/>
     </row>
     <row r="60" spans="1:17">
-      <c r="B60" s="284" t="s">
+      <c r="B60" s="281" t="s">
         <v>83</v>
       </c>
-      <c r="C60" s="284"/>
-      <c r="D60" s="284"/>
-      <c r="E60" s="284"/>
-      <c r="F60" s="284"/>
-      <c r="G60" s="284"/>
-      <c r="H60" s="284"/>
-      <c r="I60" s="284"/>
-      <c r="J60" s="284"/>
-      <c r="K60" s="284"/>
-      <c r="L60" s="284"/>
-      <c r="M60" s="284"/>
-      <c r="N60" s="284"/>
-      <c r="O60" s="284"/>
-      <c r="P60" s="284"/>
+      <c r="C60" s="281"/>
+      <c r="D60" s="281"/>
+      <c r="E60" s="281"/>
+      <c r="F60" s="281"/>
+      <c r="G60" s="281"/>
+      <c r="H60" s="281"/>
+      <c r="I60" s="281"/>
+      <c r="J60" s="281"/>
+      <c r="K60" s="281"/>
+      <c r="L60" s="281"/>
+      <c r="M60" s="281"/>
+      <c r="N60" s="281"/>
+      <c r="O60" s="281"/>
+      <c r="P60" s="281"/>
       <c r="Q60" s="57"/>
     </row>
     <row r="61" spans="1:17">
@@ -7147,21 +7152,21 @@
       </c>
     </row>
     <row r="70" spans="2:17">
-      <c r="B70" s="284"/>
-      <c r="C70" s="284"/>
-      <c r="D70" s="284"/>
-      <c r="E70" s="284"/>
-      <c r="F70" s="284"/>
-      <c r="G70" s="284"/>
-      <c r="H70" s="284"/>
-      <c r="I70" s="284"/>
-      <c r="J70" s="284"/>
-      <c r="K70" s="284"/>
-      <c r="L70" s="284"/>
-      <c r="M70" s="284"/>
-      <c r="N70" s="284"/>
-      <c r="O70" s="284"/>
-      <c r="P70" s="284"/>
+      <c r="B70" s="281"/>
+      <c r="C70" s="281"/>
+      <c r="D70" s="281"/>
+      <c r="E70" s="281"/>
+      <c r="F70" s="281"/>
+      <c r="G70" s="281"/>
+      <c r="H70" s="281"/>
+      <c r="I70" s="281"/>
+      <c r="J70" s="281"/>
+      <c r="K70" s="281"/>
+      <c r="L70" s="281"/>
+      <c r="M70" s="281"/>
+      <c r="N70" s="281"/>
+      <c r="O70" s="281"/>
+      <c r="P70" s="281"/>
       <c r="Q70" s="57"/>
     </row>
     <row r="71" spans="2:17">
